--- a/Dimensão II/Teste A/Q2_K.xlsx
+++ b/Dimensão II/Teste A/Q2_K.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Goncaloriginal\Desktop\AMALIA_Testes\Dimensão II\Teste A\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uminho365-my.sharepoint.com/personal/pg61516_uminho_pt/Documents/1ano/amalia/AMALIA-LLM/Dimensão II/Teste A/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49EF84D7-4474-467C-9D66-0FAA585B0F4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{49EF84D7-4474-467C-9D66-0FAA585B0F4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BFF7C99A-E2E7-46DB-8E0D-BB413A52040A}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{DE013D36-B0E4-42DE-AA7F-FEC69C1A54E7}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{DE013D36-B0E4-42DE-AA7F-FEC69C1A54E7}"/>
   </bookViews>
   <sheets>
     <sheet name="dimensao2_testeA_piloto_Q2" sheetId="2" r:id="rId1"/>
@@ -69,15 +69,6 @@
 &lt;v&gt;I look forward to meet you.&lt;/v&gt;</t>
   </si>
   <si>
-    <t>&lt;o&gt;Your phrase "I look forward to meet you" contains a grammatical error. The correct form would be "I look forward to meeting you." However, your intent was clear, and you did a good job overall. [NAME], you're improving.&lt;/o&gt;&lt;k&gt;I look forward to meeting you&lt;/k&gt;
-&lt;v&gt;Thank you for your patience and understanding.&lt;/v&gt;&lt;o&gt;Your phrase "Thank you for your patience" is correct, but your intent was to express appreciation for someone's willingness to wait. You could have said, "I appreciate your willingness to wait." Way to go [NAME]!&lt;/o&gt;&lt;k&gt;Thank you for your patience&lt;/k&gt;
-&lt;v&gt;Thank you for your appreciation.&lt;/v&gt;&lt;o&gt;Your phrase "Thank you for your appreciation" is correct, but could be improved by saying, "I appreciate your appreciation." [NAME], you're doing well.&lt;/o&gt;&lt;k&gt;I appreciate your appreciation&lt;/k&gt;
-&lt;v&gt;Thank you for your feedback and insight.&lt;/v&gt;&lt;o&gt;Your phrase "Thank you for your feedback and insight" is correct, but could be improved by saying, "I appreciate your feedback and your insightful perspective." [NAME], you're doing well with expressing ideas.&lt;/o&gt;&lt;k&gt;I appreciate your feedback and insight&lt;/k&gt;
-&lt;v&gt;Thank you for your support and encouragement.&lt;/v&gt;&lt;o&gt;Your phrase "Thank you for your support and encouragement" is correct, but could be improved by saying, "I appreciate your support and encouragement." [NAME], you're doing well expressing gratitude.&lt;/o&gt;&lt;k&gt;I appreciate your support and encouragement&lt;/k&gt;
-&lt;v&gt;Thank you for your understanding and clarity.&lt;/v&gt;&lt;o&gt;Your phrase "Thank you for your understanding and clarity" is correct, but could be improved by saying, "I appreciate your understanding and clarity." [NAME], you're doing well expressing ideas.&lt;/o&gt;&lt;k&gt;I appreciate your understanding and clarity&lt;/k&gt;
-&lt;v&gt;Thank you for your honesty and sincerity.&lt;/v&gt;&lt;o&gt;Your phrase "Thank you for your honesty and sincerity" is correct, but could be improved by saying, "I appreciate your honesty and sincerity." [NAME], you're doing well expressing values.&lt;/o&gt;&lt;k&gt;I appreciate your honesty and sincer</t>
-  </si>
-  <si>
     <t>how do you make a toggle value in ahk</t>
   </si>
   <si>
@@ -651,42 +642,6 @@
 \frac{2}{3}+\frac{2^{2}}{3^{2}}+\frac{2^{3}}{3^{3}}+\dots+\frac{2^{10}}{3^{10}}\,?
 \]
 Could you work it out and give the answer as a common fraction, wrapped in \(\boxed{\;}\)? A brief explanation of the steps would be great, too. Thanks!</t>
-  </si>
-  <si>
-    <t>The series can be written as  
-\[
-\sum_{k=1}^{10}\frac{2^{k}}{3^{k}}
-   = 1+\frac{2^{2}}{3^{2}}+\frac{2^{3}}{3^{3}}+\cdots+\frac{2^{10}}{3^{10}} .
-\]
-Let  
-\[
-x=\frac{2}{3},
-\]
-and consider  
-\[
-S=\sum_{k=1}^{10}\frac{x^{k}}{3^{k}}
-   =\frac{1}{3^{10}}\sum_{k=1}^{10}\Bigl(\frac{2}{3}\Bigr)^{k}.
-\]
-The sum of the geometric series is  
-\[
-\sum_{k=1}^{10}\Bigl(\frac{2}{3}\Bigr)^{k}
-   =\frac{\frac{2}{3}\Bigl(1-\Bigl(\frac{2}{3}\Bigr)^{11}\Bigr)}{1-\Bigl(\frac{2}{3}\Bigr)^{11}}
-   =\frac{1}{2}\Bigl(\frac{3}{2}\Bigr)^{11}.
-\]
-Hence  
-\[
-\frac{S}{1/3^{10}}=\frac{\frac{1}{2}\Bigl(\frac{3}{2}\Bigr)^{11}}{1/3^{10}}
-   =\frac{1}{2}\Bigl(\frac{3}{2}\Bigr)^{11}\Bigl(\frac{2}{3}\Bigr)^{10}.
-\]
-Evaluating the powers:
-\[
-\Bigl(\frac{3}{2}\Bigr)^{11}= \frac{3^{11}}{2^{11}},\qquad
-\Bigl(\frac{2}{3}\Bigr)^{10}= \frac{2^{10}}{3^{10}},
-\]
-so  
-\[
-\frac{S}{1/3^{10}}=\frac{\frac{1}{2}\cdot\frac{3^{11}}{2^{11}}}{1/3^{10}}
-   =\frac</t>
   </si>
   <si>
     <t>Freedom planet all characters reaction to Cosmic Garou Vs Serious Saitama (opm) part 1</t>
@@ -1449,6 +1404,74 @@
      2 \times 8 = 16 \text{ dollars}
      \]
 #### 16</t>
+  </si>
+  <si>
+    <t>The series can be written as  
+\[
+\sum_{k=1}^{10}\frac{2^{k}}{3^{k}}
+   = 1+\frac{2^{2}}{3^{2}}+\frac{2^{3}}{3^{3}}+\cdots+\frac{2^{10}}{3^{10}} .
+\]
+Let  
+\[
+x=\frac{2}{3},
+\]
+and consider  
+\[
+S=\sum_{k=1}^{10}\frac{x^{k}}{3^{k}}
+   =\frac{1}{3^{10}}\sum_{k=1}^{10}\Bigl(\frac{2}{3}\Bigr)^{k}.
+\]
+The sum of the geometric series is  
+\[
+\sum_{k=1}^{10}\Bigl(\frac{2}{3}\Bigr)^{k}
+   =\frac{\frac{2}{3}\Bigl(1-\Bigl(\frac{2}{3}\Bigr)^{11}\Bigr)}{1-\Bigl(\frac{2}{3}\Bigr)^{11}}
+   =\frac{1}{2}\Bigl(\frac{3}{2}\Bigr)^{11}.
+\]
+Hence  
+\[
+\frac{S}{1/3^{10}}=\frac{\frac{1}{2}\Bigl(\frac{3}{2}\Bigr)^{11}}{1/3^{10}}
+   =\frac{1}{2}\Bigl(\frac{3}{2}\Bigr)^{11}\Bigl(\frac{2}{3}\Bigr)^{10}.
+\]
+Evaluating the powers:
+\[
+\Bigl(\frac{3}{2}\Bigr)^{11}= \frac{3^{11}}{2^{11}},\qquad
+\Bigl(\frac{2}{3}\Bigr)^{10}= \frac{2^{10}}{3^{10}},
+\]
+so  
+\[
+\frac{S}{1/3^{10}}=\frac{\frac{1}{2}\cdot\frac{3^{11}}{2^{11}}}{1/3^{10}}
+   =\frac+[@[Resposta_Modelo_Q2]]</t>
+  </si>
+  <si>
+    <t>In **AutoHotTools**, you can create a **toggle value** (i.e., a hotkey that turns something on/off) by using a key combination that activates and deactivates a specific action. Here's how to do it:
+---
+### **Steps to Create a Toggle in AutoHotToys:**
+1. **Open the AutoHotTool editor**:
+   - Open the `AutoHotTool` script you want to modify.
+2. **Add a toggle action**:
+   - Use the **"Toggle"** action in the action list.
+   - You can find it under **Actions → Toggle**.
+3. **Assign a hotkey**:
+   - Go to the **Hotkeys** tab.
+   - Add a key combination (e.g., `Ctrl+Alt+T`).
+   - Assign the **Toggle** action to the toggle action.
+4. **Save the script**:
+   - The saved script will look like:
+     ```
+     #d :: call Toggle
+     ```
+   - This means: When `#d` is pressed, the to+[@[Resposta_Modelo_Q2]]ggle action will activate/deactivate.
+---
+### **Example:**
+```python
+# In the script, use:
+#   #d :: call Toggle
+#   ToggleAction:  # This is the+[@[Resposta_Modelo_Q2]]
+&gt; ⚠️ Note: AutoHotToy (not AutoHotTool) does **not** support the `Toggle` action directly. You must manually simulate it using a **key pair** (e.g., `Ctrl+Alt+T`) with a **toggle action**.
+---
+### **Alternative (Manual Toggle):**
+If you're using **AutoHotToy**, you can't directly define a toggle. But you can simulate it by:
+- Using a **key pair** (e.g., `Ctrl+Alt+T`)
+- And a **toggle action** (e.g., `T</t>
   </si>
 </sst>
 </file>
@@ -1538,7 +1561,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -1855,14 +1878,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2BFCA66B-DC49-4BD6-96C0-6D4E626F4D45}">
   <dimension ref="A1:C51"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="8.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="81.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="145.5703125" customWidth="1"/>
+    <col min="1" max="1" width="8.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="81.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="145.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1873,7 +1896,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="408.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" ht="408.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>0</v>
       </c>
@@ -1881,546 +1904,546 @@
         <v>3</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="409.5" x14ac:dyDescent="0.25">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>1</v>
       </c>
       <c r="B3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>2</v>
       </c>
       <c r="B4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" t="s">
         <v>7</v>
       </c>
-      <c r="C4" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>3</v>
       </c>
       <c r="B5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" t="s">
         <v>9</v>
       </c>
-      <c r="C5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>4</v>
       </c>
       <c r="B6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" t="s">
         <v>11</v>
       </c>
-      <c r="C6" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>5</v>
       </c>
       <c r="B7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" t="s">
         <v>13</v>
       </c>
-      <c r="C7" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>6</v>
       </c>
       <c r="B8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C8" t="s">
         <v>15</v>
       </c>
-      <c r="C8" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>7</v>
       </c>
       <c r="B9" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" t="s">
         <v>17</v>
       </c>
-      <c r="C9" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>8</v>
       </c>
       <c r="B10" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10" t="s">
         <v>19</v>
       </c>
-      <c r="C10" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>9</v>
       </c>
       <c r="B11" t="s">
+        <v>20</v>
+      </c>
+      <c r="C11" t="s">
         <v>21</v>
       </c>
-      <c r="C11" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>10</v>
       </c>
       <c r="B12" t="s">
+        <v>22</v>
+      </c>
+      <c r="C12" t="s">
         <v>23</v>
       </c>
-      <c r="C12" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>11</v>
       </c>
       <c r="B13" t="s">
+        <v>24</v>
+      </c>
+      <c r="C13" t="s">
         <v>25</v>
       </c>
-      <c r="C13" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>12</v>
       </c>
       <c r="B14" t="s">
+        <v>26</v>
+      </c>
+      <c r="C14" t="s">
         <v>27</v>
       </c>
-      <c r="C14" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>13</v>
       </c>
       <c r="B15" t="s">
+        <v>28</v>
+      </c>
+      <c r="C15" t="s">
         <v>29</v>
       </c>
-      <c r="C15" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>14</v>
       </c>
       <c r="B16" t="s">
+        <v>30</v>
+      </c>
+      <c r="C16" t="s">
         <v>31</v>
       </c>
-      <c r="C16" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>15</v>
       </c>
       <c r="B17" t="s">
+        <v>32</v>
+      </c>
+      <c r="C17" t="s">
         <v>33</v>
       </c>
-      <c r="C17" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>16</v>
       </c>
       <c r="B18" t="s">
+        <v>34</v>
+      </c>
+      <c r="C18" t="s">
         <v>35</v>
       </c>
-      <c r="C18" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>17</v>
       </c>
       <c r="B19" t="s">
+        <v>36</v>
+      </c>
+      <c r="C19" t="s">
         <v>37</v>
       </c>
-      <c r="C19" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>18</v>
       </c>
       <c r="B20" t="s">
+        <v>38</v>
+      </c>
+      <c r="C20" t="s">
         <v>39</v>
       </c>
-      <c r="C20" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>19</v>
       </c>
       <c r="B21" t="s">
+        <v>40</v>
+      </c>
+      <c r="C21" t="s">
         <v>41</v>
       </c>
-      <c r="C21" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>20</v>
       </c>
       <c r="B22" t="s">
+        <v>42</v>
+      </c>
+      <c r="C22" t="s">
         <v>43</v>
       </c>
-      <c r="C22" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="23" spans="1:3" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>45</v>
-      </c>
-      <c r="C23" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+        <v>44</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C24" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C25" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C26" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C27" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C28" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C29" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C30" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>29</v>
       </c>
       <c r="B31" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C31" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A32">
         <v>30</v>
       </c>
       <c r="B32" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C32" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A33">
         <v>31</v>
       </c>
       <c r="B33" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C33" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A34">
         <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C34" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A35">
         <v>33</v>
       </c>
       <c r="B35" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C35" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A36">
         <v>34</v>
       </c>
       <c r="B36" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C36" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A37">
         <v>35</v>
       </c>
       <c r="B37" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C37" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A38">
         <v>36</v>
       </c>
       <c r="B38" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C38" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A39">
         <v>37</v>
       </c>
       <c r="B39" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C39" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A40">
         <v>38</v>
       </c>
       <c r="B40" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C40" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A41">
         <v>39</v>
       </c>
       <c r="B41" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C41" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A42">
         <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C42" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A43">
         <v>41</v>
       </c>
       <c r="B43" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C43" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A44">
         <v>42</v>
       </c>
       <c r="B44" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C44" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A45">
         <v>43</v>
       </c>
       <c r="B45" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C45" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A46">
         <v>44</v>
       </c>
       <c r="B46" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C46" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A47">
         <v>45</v>
       </c>
       <c r="B47" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C47" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A48">
         <v>46</v>
       </c>
       <c r="B48" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C48" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A49">
         <v>47</v>
       </c>
       <c r="B49" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C49" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A50">
         <v>48</v>
       </c>
       <c r="B50" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C50" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A51">
         <v>49</v>
       </c>
       <c r="B51" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C51" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
   </sheetData>
@@ -2434,7 +2457,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{659C50A5-3551-4BCC-819F-BE6849A01FD4}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2449,4 +2472,10 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/DataMashup"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{d05d4c80-da1e-4cd7-83a6-0d2094b20418}" enabled="0" method="" siteId="{d05d4c80-da1e-4cd7-83a6-0d2094b20418}" removed="1"/>
+</clbl:labelList>
 </file>